--- a/pcb/robot/gerbers/BOM_JLCPCB.xlsx
+++ b/pcb/robot/gerbers/BOM_JLCPCB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JHORDAN\FREELANCE\PROYECTOS\KICAD_USB_PD_MODULAR\Github\smartphone-robot-cad\pcb\robot\gerbers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0387F823-69C5-4282-AF97-632D9C2997BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D01544-D5D4-4C39-94B5-A52D4031F586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="233">
   <si>
     <t>Comment</t>
   </si>
@@ -41,7 +41,7 @@
         <sz val="11"/>
         <color rgb="FFAFABAB"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>JLCPCB Part #</t>
     </r>
@@ -59,7 +59,7 @@
         <sz val="11"/>
         <color rgb="FFAFABAB"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>optional</t>
     </r>
@@ -756,6 +756,9 @@
   </si>
   <si>
     <t>No replace</t>
+  </si>
+  <si>
+    <t>TJ-S1706SW6TGLC2G-A5</t>
   </si>
 </sst>
 </file>
@@ -773,20 +776,20 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFAFABAB"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1750,7 +1753,7 @@
         <v>207</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>212</v>
